--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569454441</v>
+        <v>46157.93101489755</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101489755</v>
+        <v>46157.93174970089</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93174970089</v>
+        <v>46157.93401033754</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401033754</v>
+        <v>46157.93718981827</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718981827</v>
+        <v>46158.28217207509</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217207509</v>
+        <v>46158.29682810834</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682810834</v>
+        <v>46158.29815801022</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815801022</v>
+        <v>46158.33388211452</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388211452</v>
+        <v>46158.36858034788</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Новая папка/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858034788</v>
+        <v>46158.3728865836</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
